--- a/daily_matches/job_matches_2026-10-13.xlsx
+++ b/daily_matches/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applications Development Programmer Analyst I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tucson, AZ, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, EC2, FastAPI, Docker, CI/CD, GitHub Actions, Git, PySpark</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
+          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | Contract | Remote</t>
+          <t>Python- AI Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech Holding</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Glue, Kubernetes, Git, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,42 +544,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>BigQuery, Dataflow, Docker, Kubernetes, Jenkins, Git, BigQuery, Kafka, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software and AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, FastAPI, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,14 +589,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c342ed77660318b</t>
+          <t>https://www.indeed.com/viewjob?jk=10c309be1a9530e1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -610,46 +610,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, S3, Glue, CI/CD, PostgreSQL, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer- Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python</t>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
+          <t>https://www.indeed.com/viewjob?jk=193ed9134bb0ba66</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software and AI Engineer</t>
+          <t>Software Engineering Senior</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, FastAPI, CI/CD, Git, Python, R</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,67 +694,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1860da7c7ef419</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c8e4f18a24c446</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineering – New College Graduate 2027</t>
+          <t>Software Engineer, Agentic Runtime</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Glean Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, Kubernetes, Git, Kafka, Python, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d4f6a88e900738b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d97e6ed928b0d0d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applications Development Sr Programmer Analyst - C12 - IRVING</t>
+          <t>Distinguished Engineer - ML/AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, PyTorch, scikit-learn, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,137 +764,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c51bbbebbb910c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6b8f1042f51151</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineering II</t>
+          <t>Sr Cloud Data and AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Columbus, OH, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Copilot, BigQuery, Kubernetes, Git, BigQuery, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf934a0b837a961</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea05809be51404</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Advanced R&amp;D Engineer/Scientist</t>
+          <t>Data Scientist (Houston, Texas)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Solstice Advanced Materials</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, NoSQL, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b956945b16d4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd9499e69d161b6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Data Scientist Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, PySpark, Python, SQL, R, C++, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e093a2fa8cda192b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a865acf50ca112f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AWS Developer (Java Spring Boot) 6454565</t>
+          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,637 +904,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84eea5a116c880ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c748872238006977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Analyst</t>
+          <t>HPE Factory Build Process -DevID Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr Cloud Data and AI Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hartford, CT, USA USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5101d45ffa363462</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI Engineer – Founding Member, NJ Office</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nu Image Medical</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, USA USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f982f21a85df636</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Engineer - Senior</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MXI</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4f2d8209699c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer IV</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Application Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nashville, TN, USA USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c224b0864e1f801</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Unsecured Installments</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Upstart</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=699d1d858352b385</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Basking Ridge, NJ, USA USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, GitHub Actions, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fe747affb74da55</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Knowledge Graph Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BioAge Labs</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, FastAPI, Git, BigQuery, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de465ee91f4692db</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Associate AI Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NAVEX</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Houston, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, scikit-learn, CI/CD, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3192632de7b14325</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer–Artificial Intelligence (Mid-Level, Senior)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Berkeley, MO, USA USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Tableau, Python, SQL, R, Java, C++</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca8a8f259929e3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Management and Database Administration Specialist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Trellis Company</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Intuitive Machines</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CI/CD, MySQL, NoSQL, Python, SQL, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94fef9674c25c7cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Architech</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Meeru AI Inc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Pinecone, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bd0260b30b11aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SpaceXSI</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01e5c451d37cbdd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Plastic Labs - Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>deCircle</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, S3, FastAPI, Docker, Kubernetes, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e862cbea853f93a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Salesforce</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Intermountain Health</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Murray, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76be51f0ada30d</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Associate Data Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Westport Properties, Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=608f5264aa9fa6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd1dbef9ba182fe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-13.xlsx
+++ b/daily_matches/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Burbank, CA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, RAG, PyTorch, scikit-learn, XGBoost, LightGBM, BigQuery, MLflow, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
+          <t>https://www.indeed.com/viewjob?jk=0c48a772b155e740</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python- AI Software Engineer III</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, Git, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6517d29fbe4469e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>US- Java Engineer - Pricing</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MoneyGram</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Docker, Kubernetes, Jenkins, Git, BigQuery, Kafka, PostgreSQL, NoSQL</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Synapse, CI/CD, Git, Databricks, PySpark, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
+          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software and AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, FastAPI, CI/CD, Git, Python, R</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c309be1a9530e1</t>
+          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Alaris Acquisitions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Data Lake, Databricks, PySpark, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8a710df9a388f1</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193ed9134bb0ba66</t>
+          <t>https://www.indeed.com/viewjob?jk=7f49fdbe9c168bcc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineering Senior</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Sensata Technologies, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Attleboro, MA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, MongoDB, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c8e4f18a24c446</t>
+          <t>https://www.indeed.com/viewjob?jk=b54f8a0116ecb069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Agentic Runtime</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Glean Technologies</t>
+          <t>Sensata Technologies, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Attleboro, MA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Kubernetes, Git, Kafka, Python, R, Java, C++, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d97e6ed928b0d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=74030a622c721f59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - ML/AI Engineer</t>
+          <t>Data Scientist AI - L3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>California, MO, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, PyTorch, scikit-learn, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, Hugging Face, PyTorch, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6b8f1042f51151</t>
+          <t>https://www.indeed.com/viewjob?jk=14ace1011dfc972c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Cloud Data and AI Engineer</t>
+          <t>AI-Focused Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>osp labs hiring for us based mnc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>Odessa, TX, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea05809be51404</t>
+          <t>https://www.indeed.com/viewjob?jk=34cfc642b4f39834</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist (Houston, Texas)</t>
+          <t>Software Engineer Agentic AI &amp; Full Stack Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>InfoZen Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Columbus, OH, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd9499e69d161b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8eab151e10dbc21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist Analyst</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NAVEX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, PySpark, Python, SQL, R, C++, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, scikit-learn, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a865acf50ca112f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c2788c027e4f77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
+          <t>Entry Level Software Engineer - Computer Vision</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Java, C++</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748872238006977</t>
+          <t>https://www.indeed.com/viewjob?jk=943978fb8bcceb7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HPE Factory Build Process -DevID Software Engineer</t>
+          <t>Software Engineer: Core</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, C++, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,182 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd1dbef9ba182fe</t>
+          <t>https://www.indeed.com/viewjob?jk=be02d73d22ddbea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer – Automotive Dealer Franchise Management Solutions</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1234306ef4c9e17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SpaceXSI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a65b214df7031bfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>innoVet Health, LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior AI Specialist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Austin, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c9e588716b24c27</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-13.xlsx
+++ b/daily_matches/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Systems Engineer, Data Management - East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Burbank, CA, USA USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, scikit-learn, XGBoost, LightGBM, BigQuery, MLflow, CI/CD, Snowflake</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Redshift, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c48a772b155e740</t>
+          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, NoSQL, Power BI</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6517d29fbe4469e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Localize</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Synapse, CI/CD, Git, Databricks, PySpark, NoSQL, Power BI</t>
+          <t>RAG, Gemini, Prompt Engineering, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
+          <t>https://www.indeed.com/viewjob?jk=64a275f552b9e37f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McGuireWoods LLP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, scikit-learn, Git, Hadoop, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
+          <t>https://www.indeed.com/viewjob?jk=e408a102a7d3920d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>System Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alaris Acquisitions</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Richardson, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Data Lake, Databricks, PySpark, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8a710df9a388f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b4231a46a18716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f49fdbe9c168bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=12db5b07809dddaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Security Engineer (Application Security)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sensata Technologies, Inc.</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Attleboro, MA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Databricks, Python, SQL, R</t>
+          <t>Generative AI, Cortex, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54f8a0116ecb069</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate Software Engineer, AI Solutions</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sensata Technologies, Inc.</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Attleboro, MA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74030a622c721f59</t>
+          <t>https://www.indeed.com/viewjob?jk=6790deaac24d043b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist AI - L3</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>California, MO, USA USA</t>
+          <t>Charlottesville, VA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, PyTorch, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ace1011dfc972c</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7130fbafa2f19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI-Focused Software Engineer</t>
+          <t>Analytics Platform Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>osp labs hiring for us based mnc</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Odessa, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, CI/CD, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34cfc642b4f39834</t>
+          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer Agentic AI &amp; Full Stack Development</t>
+          <t>Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>InfoZen Inc</t>
+          <t>IWCO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>Chanhassen, MN, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Copilot, XGBoost, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8eab151e10dbc21</t>
+          <t>https://www.indeed.com/viewjob?jk=3cac6f8708b37e2a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAVEX</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, scikit-learn, CI/CD, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Data Lake, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c2788c027e4f77</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer - Computer Vision</t>
+          <t>Senior Software Engineer: Back-end</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Java, C++</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943978fb8bcceb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=783170ffbfd7a23f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer: Core</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, C++, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be02d73d22ddbea6</t>
+          <t>https://www.indeed.com/viewjob?jk=bcde27f750358cf5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer – Automotive Dealer Franchise Management Solutions</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1234306ef4c9e17</t>
+          <t>https://www.indeed.com/viewjob?jk=eeab279103fab44c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
+          <t>Senior Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, PyTorch, scikit-learn, LightGBM, Keras, Git, Snowflake, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65b214df7031bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=b09aab72bdba8737</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer, New Verticals Agentic Foundations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
+          <t>https://www.indeed.com/viewjob?jk=b4680206820b45c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Web Site Developer Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, AKS, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>Kipsu</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Minneapolis, MN, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,7 +1114,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9e588716b24c27</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ee40910f87c61a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer, Internal Tools</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Northcloud</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, AKS, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6082be1dd3bb739</t>
         </is>
       </c>
     </row>
